--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>76.79161071777344</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78.18000030517578</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.388389587402344</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.775888439476544</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.084146076565623</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>78.35911560058594</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>76.793808,76.830627,76.772858,76.755699,76.775208,76.791611</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>76.150002,77.070000,77.720001,77.570000,77.790001,78.180000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.643806,0.239373,0.947143,0.814301,1.014793,1.388389</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.845445,0.310591,1.218661,1.049762,1.304529,1.775888</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.084146076565623</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>76.840500,76.791809,76.745331,76.692589,76.773254,76.700623</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>76.279320,76.212708,75.977516,75.843735,75.701157,75.646416</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>78.245956,78.289734,78.252411,78.347046,78.315979,78.359116</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>78.277069,78.142792,78.172989,78.269135,78.241760,78.134430</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>77.441147,77.195969,76.814682,76.632248,76.474319,76.298141</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>77.707657,77.653305,77.389984,77.348740,77.172379,77.098434</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>78.35911560058594</v>
+      </c>
+      <c r="G3" t="n">
+        <v>78.09999847412109</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2591171264648438</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3317760967059478</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3221320650404305</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:30:02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>78.19297790527344</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>78.245956,78.289734,78.252411,78.347046,78.315979,78.359116</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78.510002,78.320000,78.099998,77.820000,78.040001,78.099998</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.264046,0.030266,0.152413,0.527046,0.275978,0.259118</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.336322,0.038644,0.195150,0.677263,0.353637,0.331777</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3221320650404305</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>78.277069,78.142792,78.172989,78.269135,78.241760,78.134430</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>77.707657,77.653305,77.389984,77.348740,77.172379,77.098434</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:30:02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>78.076599,78.139557,78.109253,78.195618,78.128319,78.192978</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>77.996506,77.948112,78.117393,78.117989,78.017204,78.024513</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>77.421486,77.270813,77.046852,76.971336,76.803146,76.745743</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>77.697174,77.625854,77.476044,77.498413,77.328842,77.319733</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>78.19297790527344</v>
+      </c>
+      <c r="G4" t="n">
+        <v>77.61000061035156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.582977294921875</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.75116259546082</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7060699530507076</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:35:02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77.59849548339844</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>78.076599,78.139557,78.109253,78.195618,78.128319,78.192978</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>77.050003,77.510002,78.419998,77.639999,77.949997,77.610001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.026596,0.629555,0.310745,0.555619,0.178322,0.582977</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.332376,0.812224,0.396258,0.715634,0.228765,0.751163</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7060699530507076</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>77.996506,77.948112,78.117393,78.117989,78.017204,78.024513</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>77.697174,77.625854,77.476044,77.498413,77.328842,77.319733</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:35:02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>77.657539,77.690643,77.658585,77.644020,77.587532,77.598495</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>77.607040,77.511688,77.768661,77.611214,77.485191,77.460335</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>76.968590,76.788628,76.569908,76.369423,76.225204,76.103958</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>77.260513,77.176147,77.004013,76.927551,76.768845,76.713112</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>77.59849548339844</v>
+      </c>
+      <c r="G5" t="n">
+        <v>75.84999847412109</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.748497009277344</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.305203750101465</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.626660473798071</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>75.71913909912109</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>77.657539,77.690643,77.658585,77.644020,77.587532,77.598495</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>77.120003,77.620003,76.320000,75.690002,75.820000,75.849998</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.537536,0.070640,1.338585,1.954018,1.767532,1.748497</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.697013,0.091008,1.753912,2.581606,2.331222,2.305203</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.626660473798071</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>77.607040,77.511688,77.768661,77.611214,77.485191,77.460335</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>77.260513,77.176147,77.004013,76.927551,76.768845,76.713112</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>75.791893,75.759270,75.696594,75.662392,75.691849,75.719139</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>75.777855,75.798042,75.807060,75.740486,75.774399,75.689224</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>74.969353,74.716171,74.433578,74.189560,74.085159,73.950859</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>75.282814,75.160423,74.911690,74.818878,74.674049,74.633202</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>75.71913909912109</v>
+      </c>
+      <c r="G6" t="n">
+        <v>74.16999816894531</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.549140930175781</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.088635524362734</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.737514320919744</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>74.14856719970703</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>75.791893,75.759270,75.696594,75.662392,75.691849,75.719139</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>76.029999,75.139999,73.959999,73.870003,73.900002,74.169998</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.238106,0.619271,1.736595,1.792389,1.791847,1.549141</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.313173,0.824156,2.348019,2.426410,2.424692,2.088635</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.737514320919744</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>75.777855,75.798042,75.807060,75.740486,75.774399,75.689224</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>75.282814,75.160423,74.911690,74.818878,74.674049,74.633202</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>74.222755,74.191513,74.212486,74.159935,74.145874,74.148567</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>74.196098,74.262268,74.284294,74.322235,74.325264,74.319626</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>73.116653,72.845688,72.728981,72.491722,72.358040,72.216118</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>73.546196,73.392204,73.283684,73.148430,73.029900,72.920631</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>74.14856719970703</v>
+      </c>
+      <c r="G7" t="n">
+        <v>74.91999816894531</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7714309692382812</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.029672968622739</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5026787922286882</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>75.16914367675781</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>74.222755,74.191513,74.212486,74.159935,74.145874,74.148567</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>73.730003,73.860001,74.110001,74.510002,74.339996,74.919998</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.492752,0.331512,0.102485,0.350067,0.194122,0.771431</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.668319,0.448839,0.138288,0.469826,0.261128,1.029673</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5026787922286882</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>74.196098,74.262268,74.284294,74.322235,74.325264,74.319626</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>73.546196,73.392204,73.283684,73.148430,73.029900,72.920631</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>74.919853,75.026550,75.101784,75.136696,75.165512,75.169144</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>74.865440,75.105843,75.128517,75.234039,75.231133,75.272713</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>73.822479,73.697586,73.611465,73.482330,73.415787,73.261909</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>74.231735,74.208824,74.155121,74.119240,74.046341,73.939438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>75.16914367675781</v>
+      </c>
+      <c r="G8" t="n">
+        <v>76.30999755859375</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.140853881835938</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.495025446646026</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7373609013184792</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>76.63884735107422</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>74.919853,75.026550,75.101784,75.136696,75.165512,75.169144</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>74.820000,74.889999,75.430000,75.279999,76.690002,76.309998</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.099853,0.136551,0.328216,0.143303,1.524490,1.140854</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.133458,0.182335,0.435127,0.190360,1.987861,1.495025</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7373609013184792</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>74.865440,75.105843,75.128517,75.234039,75.231133,75.272713</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>74.231735,74.208824,74.155121,74.119240,74.046341,73.939438</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>76.400482,76.490929,76.578598,76.606590,76.663124,76.638847</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>76.377106,76.516724,76.566994,76.668633,76.714790,76.667114</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>75.452148,75.313370,75.232292,75.101044,75.069420,74.876549</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>75.786682,75.752663,75.709557,75.661026,75.598320,75.480873</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>76.63884735107422</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.26999664306641</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.368850708007812</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.597858417298848</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.798914256917148</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>73.67169189453125</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>76.400482,76.490929,76.578598,76.606590,76.663124,76.638847</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>76.400002,76.449997,75.199997,75.930000,74.129997,73.269997</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.000480,0.040932,1.378601,0.676590,2.533127,3.368850</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.000629,0.053541,1.833246,0.891070,3.417141,4.597858</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.798914256917148</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>76.377106,76.516724,76.566994,76.668633,76.714790,76.667114</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>75.786682,75.752663,75.709557,75.661026,75.598320,75.480873</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>73.398735,73.452347,73.533234,73.603241,73.645493,73.671692</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>73.451073,73.586472,73.618774,73.737732,73.959381,73.973633</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>72.073074,71.773117,71.562531,71.435593,71.308830,71.144974</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>72.591385,72.437363,72.304558,72.264542,72.165283,72.099487</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>73.67169189453125</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.33999633789062</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.331695556640625</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4522710297290494</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5993006940567227</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:51</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>73.62953948974609</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>73.398735,73.452347,73.533234,73.603241,73.645493,73.671692</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>73.209999,73.120003,74.269997,74.230003,73.209999,73.339996</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.188736,0.332344,0.736763,0.626762,0.435494,0.331696</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.257801,0.454519,0.992006,0.844352,0.594856,0.452271</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5993006940567227</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>73.451073,73.586472,73.618774,73.737732,73.959381,73.973633</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>72.591385,72.437363,72.304558,72.264542,72.165283,72.099487</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:51</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>73.336166,73.386879,73.408119,73.500992,73.547600,73.629539</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>73.364647,73.449806,73.542793,73.571541,73.800102,73.807404</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>72.068283,71.829529,71.552834,71.361176,71.291809,71.143486</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>72.521980,72.441071,72.250534,72.253456,72.155800,72.103928</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>73.62953948974609</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.76999664306641</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1404571533203125</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1903987524899989</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6010149846869317</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>74.57542419433594</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>73.336166,73.386879,73.408119,73.500992,73.547600,73.629539</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>74.160004,73.870003,73.040001,72.669998,73.550003,73.769997</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.823838,0.483124,0.368118,0.830994,0.002403,0.140458</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.110892,0.654019,0.503995,1.143517,0.003267,0.190399</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6010149846869317</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>73.364647,73.449806,73.542793,73.571541,73.800102,73.807404</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>72.521980,72.441071,72.250534,72.253456,72.155800,72.103928</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>73.916725,74.072121,74.234901,74.363113,74.493599,74.575424</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>73.964951,74.125099,74.339035,74.397873,74.602814,74.720352</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>72.703636,72.604134,72.494392,72.393456,72.346146,72.266106</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>73.185204,73.176407,73.144203,73.178123,73.161194,73.139717</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>74.57542419433594</v>
+      </c>
+      <c r="G12" t="n">
+        <v>74.04000091552734</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5354232788085938</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7231540683251223</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4356578866440444</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:40:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>74.22100067138672</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>73.916725,74.072121,74.234901,74.363113,74.493599,74.575424</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>73.320000,74.120003,74.570000,74.730003,74.440002,74.040001</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.596725,0.047882,0.335099,0.366890,0.053597,0.535423</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.813864,0.064600,0.449375,0.490955,0.072000,0.723154</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4356578866440444</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>73.964951,74.125099,74.339035,74.397873,74.602814,74.720352</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>73.185204,73.176407,73.144203,73.178123,73.161194,73.139717</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:40:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>74.259209,74.190353,74.200851,74.176689,74.168472,74.221001</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>74.364891,74.220932,74.291496,74.237244,74.438286,74.641365</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>73.284996,73.047554,72.887375,72.723495,72.554405,72.538544</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>73.625893,73.442230,73.360664,73.263252,73.133179,73.113350</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>74.22100067138672</v>
+      </c>
+      <c r="G13" t="n">
+        <v>72.84999847412109</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.371002197265625</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.881952266275824</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.480213580683975</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>72.86144256591797</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>74.259209,74.190353,74.200851,74.176689,74.168472,74.221001</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>73.599998,73.489998,73.000000,73.000000,72.790001,72.849998</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.659211,0.700355,1.200851,1.176689,1.378471,1.371003</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.895666,0.952994,1.645001,1.611903,1.893764,1.881953</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.480213580683975</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>74.364891,74.220932,74.291496,74.237244,74.438286,74.641365</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>73.625893,73.442230,73.360664,73.263252,73.133179,73.113350</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>72.811958,72.617508,72.725342,72.847694,72.612206,72.861443</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>72.807854,72.682373,72.671974,73.028770,72.936066,73.431389</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>71.877304,71.460007,71.454803,71.386436,71.006943,71.096306</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>72.174019,71.933136,72.000839,71.967438,71.616501,71.720787</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>72.86144256591797</v>
+      </c>
+      <c r="G14" t="n">
+        <v>73.12000274658203</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2585601806640625</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3536107370785743</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6842324846914082</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:57</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>73.91938018798828</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>72.811958,72.617508,72.725342,72.847694,72.612206,72.861443</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>72.900002,72.830002,72.730003,71.199997,71.879997,73.120003</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.088044,0.212494,0.004661,1.647697,0.732209,0.258560</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.120773,0.291767,0.006409,2.314181,1.018654,0.353610</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6842324846914082</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>72.807854,72.682373,72.671974,73.028770,72.936066,73.431389</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>72.174019,71.933136,72.000839,71.967438,71.616501,71.720787</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:57</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>73.312050,73.300308,73.318184,73.380867,73.587753,73.919380</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>73.683029,73.300613,73.337067,73.316071,73.955841,74.711624</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>72.029099,71.768745,71.496140,71.246292,71.195473,71.346375</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>72.572937,72.440002,72.218040,72.167030,72.072960,72.269028</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>73.91938018798828</v>
+      </c>
+      <c r="G15" t="n">
+        <v>72.87000274658203</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.04937744140625</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.440067794501999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4935639470947475</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>73.29354858398438</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>73.312050,73.300308,73.318184,73.380867,73.587753,73.919380</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>73.400002,72.940002,72.970001,73.650002,73.540001,72.870003</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.087952,0.360306,0.348183,0.269135,0.047752,1.049377</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.119825,0.493975,0.477159,0.365424,0.064933,1.440068</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4935639470947475</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>73.683029,73.300613,73.337067,73.316071,73.955841,74.711624</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>72.572937,72.440002,72.218040,72.167030,72.072960,72.269028</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>72.852333,72.972527,73.083672,72.933891,73.025352,73.293549</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>73.032501,72.979546,73.389915,72.983192,73.539444,73.970039</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>71.882645,71.620079,71.544159,71.130707,71.163162,71.195740</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>72.236046,72.261414,72.293259,71.892601,71.852074,71.966156</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>73.29354858398438</v>
+      </c>
+      <c r="G16" t="n">
+        <v>73.44999694824219</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1564483642578125</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2129998240409139</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7115680913697157</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>73.40960693359375</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>72.852333,72.972527,73.083672,72.933891,73.025352,73.293549</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>72.430000,72.360001,73.540001,73.949997,73.489998,73.449997</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.422333,0.612526,0.456329,1.016106,0.464646,0.156448</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.583091,0.846499,0.620518,1.374045,0.632257,0.212999</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7115680913697157</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>73.032501,72.979546,73.389915,72.983192,73.539444,73.970039</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>72.236046,72.261414,72.293259,71.892601,71.852074,71.966156</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>73.547981,73.474579,73.438553,73.518440,73.381561,73.409607</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>73.646667,73.440376,73.513107,73.537643,73.624741,73.654137</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>72.493965,72.244263,72.035439,71.999794,71.774178,71.720467</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>72.853783,72.713013,72.576454,72.591454,72.357864,72.296677</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>73.40960693359375</v>
+      </c>
+      <c r="G17" t="n">
+        <v>73.79000091552734</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3803939819335938</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5155088456619722</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5856393856888327</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>73.92923736572266</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>73.547981,73.474579,73.438553,73.518440,73.381561,73.409607</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>73.599998,73.870003,73.919998,74.139999,74.050003,73.790001</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.052017,0.395424,0.481445,0.621559,0.668442,0.380394</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.070676,0.535297,0.651306,0.838359,0.902690,0.515509</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5856393856888327</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>73.646667,73.440376,73.513107,73.537643,73.624741,73.654137</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>72.853783,72.713013,72.576454,72.591454,72.357864,72.296677</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>73.861946,73.840469,73.837311,73.892998,73.892776,73.929237</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>73.901070,73.791435,73.878311,73.897392,74.015518,74.118431</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>72.910393,72.718185,72.512711,72.430458,72.325371,72.228348</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>73.250076,73.156471,73.016434,73.017281,72.902702,72.869827</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>73.92923736572266</v>
+      </c>
+      <c r="G18" t="n">
+        <v>73.44000244140625</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4892349243164062</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.666169537108526</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2987174372995027</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:57</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>73.78085327148438</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>73.861946,73.840469,73.837311,73.892998,73.892776,73.929237</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>73.910004,73.699997,73.889999,74.410004,73.970001,73.440002</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.048058,0.140472,0.052688,0.517006,0.077225,0.489235</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.065022,0.190600,0.071307,0.694807,0.104401,0.666169</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2987174372995027</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>73.901070,73.791435,73.878311,73.897392,74.015518,74.118431</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>73.250076,73.156471,73.016434,73.017281,72.902702,72.869827</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:57</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>73.582573,73.682182,73.698807,73.711845,73.724968,73.780853</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>73.636986,73.710289,73.762405,73.771317,73.827026,73.860611</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>72.654976,72.614655,72.495148,72.402870,72.346436,72.301178</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>73.021172,73.031067,72.942215,72.913361,72.843231,72.855850</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>73.78085327148438</v>
+      </c>
+      <c r="G19" t="n">
+        <v>72.66000366210938</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.120849609375</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.54259503562274</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9508977458037289</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:08</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>73.14231872558594</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>73.582573,73.682182,73.698807,73.711845,73.724968,73.780853</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>73.800003,73.379997,73.250000,72.739998,72.629997,72.660004</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.217430,0.302185,0.448807,0.971847,1.094971,1.120849</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.294621,0.411808,0.612706,1.336056,1.507601,1.542595</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9508977458037289</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>73.636986,73.710289,73.762405,73.771317,73.827026,73.860611</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>73.021172,73.031067,72.942215,72.913361,72.843231,72.855850</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:08</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>72.838326,72.957214,72.998367,73.035706,73.098099,73.142319</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>72.889145,73.017212,73.065994,73.137764,73.199348,73.236130</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>71.897125,71.841331,71.756668,71.671082,71.630768,71.546104</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>72.264534,72.276527,72.223846,72.214714,72.165939,72.154167</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>73.14231872558594</v>
+      </c>
+      <c r="G20" t="n">
+        <v>73.91999816894531</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.777679443359375</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.052055550085346</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.855776761830112</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>73.84107208251953</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>72.838326,72.957214,72.998367,73.035706,73.098099,73.142319</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>72.870003,73.580002,73.830002,73.970001,73.690002,73.919998</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.031677,0.622788,0.831635,0.934295,0.591903,0.777679</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.043470,0.846409,1.126419,1.263073,0.803234,1.052055</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.855776761830112</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>72.889145,73.017212,73.065994,73.137764,73.199348,73.236130</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>72.264534,72.276527,72.223846,72.214714,72.165939,72.154167</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>73.950066,73.937080,73.918396,73.924255,73.886475,73.841072</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>73.999336,73.984627,73.934517,73.955109,73.893051,73.945038</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>73.085678,72.966095,72.858627,72.839973,72.716278,72.630043</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>73.424324,73.356743,73.281776,73.262520,73.142693,73.057724</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>73.84107208251953</v>
+      </c>
+      <c r="G21" t="n">
+        <v>75.80999755859375</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.968925476074219</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.597184460469651</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.433838117067887</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>75.39797210693359</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>73.950066,73.937080,73.918396,73.924255,73.886475,73.841072</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>74.779999,75.550003,76.330002,76.089996,75.980003,75.809998</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.829933,1.612923,2.411606,2.165741,2.093528,1.968926</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.109833,2.134908,3.159447,2.846289,2.755368,2.597185</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2.433838117067887</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>73.999336,73.984627,73.934517,73.955109,73.893051,73.945038</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>73.424324,73.356743,73.281776,73.262520,73.142693,73.057724</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>75.729042,75.660500,75.639923,75.564301,75.493553,75.397972</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>75.749107,75.623177,75.647545,75.576622,75.510765,75.319252</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>74.815987,74.539879,74.316925,74.109726,73.888031,73.658821</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>75.182831,74.982536,74.817574,74.668289,74.493248,74.313919</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>75.39797210693359</v>
+      </c>
+      <c r="G22" t="n">
+        <v>76.45999908447266</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.062026977539062</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.388996848359545</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.395898744888484</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>76.02681732177734</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>75.729042,75.660500,75.639923,75.564301,75.493553,75.397972</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>76.290001,76.430000,77.360001,77.169998,76.209999,76.459999</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.560959,0.769500,1.720078,1.605697,0.716446,1.062027</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.735298,1.006804,2.223472,2.080727,0.940095,1.388997</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1.395898744888484</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>75.749107,75.623177,75.647545,75.576622,75.510765,75.319252</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>75.182831,74.982536,74.817574,74.668289,74.493248,74.313919</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>76.455772,76.351112,76.231796,76.190613,76.116570,76.026817</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>76.412933,76.265305,76.215210,76.136375,76.060448,75.948349</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>75.440094,75.118950,74.789963,74.605247,74.390617,74.153931</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>75.852425,75.600121,75.321335,75.214043,75.031303,74.861603</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>76.02681732177734</v>
+      </c>
+      <c r="G23" t="n">
+        <v>76.01999664306641</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0068206787109375</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.008972216537922718</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3513796489227918</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:15:06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>75.92764282226562</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>76.455772,76.351112,76.231796,76.190613,76.116570,76.026817</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>76.919998,76.970001,75.910004,76.110001,76.239998,76.019997</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.464226,0.618889,0.321792,0.080612,0.123428,0.006820</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.603518,0.804065,0.423913,0.105916,0.161894,0.008972</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3513796489227918</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>76.412933,76.265305,76.215210,76.136375,76.060448,75.948349</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>75.852425,75.600121,75.321335,75.214043,75.031303,74.861603</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:15:06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>75.978249,75.947716,75.926971,75.942505,75.945572,75.927643</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>75.896698,75.878410,75.892960,75.882210,75.885811,75.798187</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>74.960304,74.719391,74.516304,74.393860,74.271484,74.117332</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>75.374092,75.202362,75.038437,75.008125,74.916718,74.823433</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>75.92764282226562</v>
+      </c>
+      <c r="G24" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.572357177734375</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7481793172998366</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6079309209126806</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:52</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>76.03676605224609</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>75.978249,75.947716,75.926971,75.942505,75.945572,75.927643</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>75.620003,76.139999,74.870003,75.570000,76.150002,76.500000</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.358246,0.192283,1.056968,0.372505,0.204430,0.572357</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.473745,0.252539,1.411738,0.492927,0.268456,0.748179</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6079309209126806</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>75.896698,75.878410,75.892960,75.882210,75.885811,75.798187</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>75.374092,75.202362,75.038437,75.008125,74.916718,74.823433</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:52</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>76.359337,76.304123,76.243759,76.178986,76.117371,76.036766</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>76.298180,76.244865,76.171448,76.146645,76.025513,75.924904</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>75.432381,75.178680,74.946404,74.741913,74.542244,74.327385</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>75.804314,75.602119,75.418686,75.287582,75.123680,74.952927</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>76.03676605224609</v>
+      </c>
+      <c r="G25" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5367660522460938</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.710948413570985</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5604755881663758</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>75.37792205810547</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>76.359337,76.304123,76.243759,76.178986,76.117371,76.036766</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>76.180000,76.769997,75.680000,75.690002,75.800003,75.500000</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.179337,0.465874,0.563759,0.488984,0.317368,0.536766</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.235412,0.606843,0.744924,0.646035,0.418691,0.710948</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5604755881663758</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>76.298180,76.244865,76.171448,76.146645,76.025513,75.924904</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>75.804314,75.602119,75.418686,75.287582,75.123680,74.952927</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>75.467911,75.465675,75.456207,75.414543,75.407578,75.377922</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>75.430008,75.474167,75.429405,75.405487,75.350792,75.277336</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>74.573280,74.375977,74.188911,73.983658,73.850868,73.676857</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>74.933250,74.812355,74.676224,74.550598,74.442917,74.322922</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>75.37792205810547</v>
+      </c>
+      <c r="G26" t="n">
+        <v>76.08000183105469</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7020797729492188</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9228177655782346</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7396978693949811</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>75.97018432617188</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>75.467911,75.465675,75.456207,75.414543,75.407578,75.377922</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>76.370003,75.599998,75.580002,76.129997,76.209999,76.080002</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.902092,0.134323,0.123795,0.715454,0.802421,0.702080</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.181212,0.177677,0.163793,0.939780,1.052908,0.922818</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7396978693949811</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>75.430008,75.474167,75.429405,75.405487,75.350792,75.277336</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>74.933250,74.812355,74.676224,74.550598,74.442917,74.322922</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>76.092827,76.071609,76.036621,76.008438,75.993820,75.970184</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>76.061325,76.034210,76.017975,75.952454,75.912964,75.855804</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>75.253700,75.043365,74.841568,74.695869,74.551620,74.395325</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>75.591354,75.456978,75.302734,75.217598,75.109581,74.999725</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>75.97018432617188</v>
+      </c>
+      <c r="G27" t="n">
+        <v>75.34999847412109</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6201858520507812</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8230734765890986</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9442757988513332</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:43:06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>75.41837310791016</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>76.092827,76.071609,76.036621,76.008438,75.993820,75.970184</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>75.510002,75.440002,75.570000,74.919998,75.120003,75.349998</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.582825,0.631607,0.466621,1.088440,0.873817,0.620186</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.771851,0.837230,0.617469,1.452803,1.163228,0.823073</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9442757988513332</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>76.061325,76.034210,76.017975,75.952454,75.912964,75.855804</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>75.591354,75.456978,75.302734,75.217598,75.109581,74.999725</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:43:06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>75.386543,75.367432,75.365623,75.369225,75.390823,75.418373</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>75.384064,75.357872,75.346069,75.348534,75.342346,75.362793</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>74.615700,74.423836,74.305222,74.192467,74.130783,74.066376</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>74.918617,74.784195,74.698669,74.643066,74.609886,74.573158</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>75.41837310791016</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75.37000274658203</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.048370361328125</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.06417720520823327</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1656775975290351</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>75.35008239746094</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>75.386543,75.367432,75.365623,75.369225,75.390823,75.418373</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>75.169998,75.180000,75.449997,75.480003,75.290001,75.370003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.216545,0.187432,0.084374,0.110778,0.100822,0.048370</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.288073,0.249311,0.111828,0.146765,0.133912,0.064177</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1656775975290351</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>75.384064,75.357872,75.346069,75.348534,75.342346,75.362793</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>74.918617,74.784195,74.698669,74.643066,74.609886,74.573158</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>75.368828,75.383713,75.346840,75.351509,75.343178,75.350082</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>75.357445,75.391518,75.291756,75.295341,75.288124,75.309135</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>74.685890,74.577698,74.433220,74.355988,74.259300,74.209724</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>74.950745,74.878525,74.761879,74.727844,74.665146,74.636276</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>75.35008239746094</v>
+      </c>
+      <c r="G29" t="n">
+        <v>75.12999725341797</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2200851440429688</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2929391083306025</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3456565780349772</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:39</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>75.09738922119141</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>75.368828,75.383713,75.346840,75.351509,75.343178,75.350082</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>75.389999,75.209999,75.489998,75.160004,74.540001,75.129997</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.021171,0.173714,0.143158,0.191505,0.803177,0.220085</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.028082,0.230972,0.189638,0.254797,1.077512,0.292939</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3456565780349772</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>75.357445,75.391518,75.291756,75.295341,75.288124,75.309135</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>74.950745,74.878525,74.761879,74.727844,74.665146,74.636276</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:39</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>75.100845,75.076370,75.065781,75.094528,75.102867,75.097389</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>75.107613,75.125885,75.043488,75.076141,75.071182,75.085976</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>74.382172,74.226997,74.106262,74.041336,73.966438,73.879105</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>74.666992,74.538300,74.457420,74.442856,74.392952,74.342018</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>75.09738922119141</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75.72000122070312</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6226119995117188</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8222556649160303</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9367668117492827</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:43:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>75.52719879150391</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>75.100845,75.076370,75.065781,75.094528,75.102867,75.097389</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>75.709999,75.620003,76.029999,75.739998,75.980003,75.720001</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.609154,0.543633,0.964218,0.645470,0.877136,0.622612</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.804589,0.718901,1.268207,0.852218,1.154431,0.822256</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9367668117492827</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>75.107613,75.125885,75.043488,75.076141,75.071182,75.085976</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>74.666992,74.538300,74.457420,74.442856,74.392952,74.342018</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:43:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>75.722923,75.669373,75.603401,75.580429,75.553169,75.527199</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>75.732468,75.691788,75.591858,75.554504,75.524292,75.513107</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>75.041656,74.869682,74.697395,74.602737,74.481956,74.379311</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>75.307182,75.171745,75.029137,74.970253,74.890587,74.814781</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>75.52719879150391</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76.69000244140625</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.162803649902344</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.516238900619106</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.428995280698171</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:44</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>76.37971496582031</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>75.722923,75.669373,75.603401,75.580429,75.553169,75.527199</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>76.019997,76.250000,77.139999,77.129997,77.019997,76.690002</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.297074,0.580627,1.536598,1.549568,1.466828,1.162803</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.390784,0.761478,1.991961,2.009034,1.904476,1.516239</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1.428995280698171</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>75.732468,75.691788,75.591858,75.554504,75.524292,75.513107</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>75.307182,75.171745,75.029137,74.970253,74.890587,74.814781</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:44</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>76.611290,76.533348,76.477745,76.437042,76.406952,76.379715</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>76.638229,76.529739,76.471695,76.364243,76.349861,76.340889</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>75.880753,75.681847,75.542206,75.453911,75.388969,75.298050</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>76.140396,76.014427,75.889412,75.836403,75.766731,75.706116</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>76.37971496582031</v>
+      </c>
+      <c r="G32" t="n">
+        <v>84.95999908447266</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.580284118652344</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10.09920457993564</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6.035185463667013</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>82.48741149902344</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>76.611290,76.533348,76.477745,76.437042,76.406952,76.379715</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>76.889999,77.480003,81.790001,82.330002,85.730003,84.959999</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.278709,0.946655,5.312256,5.892960,9.323051,8.580284</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.362478,1.221806,6.494994,7.157731,10.874899,10.099205</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>6.035185463667013</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>76.638229,76.529739,76.471695,76.364243,76.349861,76.340889</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>76.140396,76.014427,75.889412,75.836403,75.766731,75.706116</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>84.425529,83.836464,83.275246,82.866829,82.645157,82.487411</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>84.206879,83.598022,83.086853,82.600090,82.303383,82.190674</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>81.635109,80.716873,79.930634,79.335953,78.963280,78.720093</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>82.625725,81.819359,81.073982,80.601784,80.218735,79.997437</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>82.48741149902344</v>
+      </c>
+      <c r="G33" t="n">
+        <v>89.16999816894531</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6.682586669921875</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.494209719799208</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.775367445109876</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:49:03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>88.67301177978516</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>84.425529,83.836464,83.275246,82.866829,82.645157,82.487411</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>86.120003,87.190002,87.320000,87.239998,87.639999,89.169998</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1.694474,3.353538,4.044754,4.373169,4.994842,6.682587</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1.967573,3.846242,4.632105,5.012803,5.699273,7.494210</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>4.775367445109876</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>84.206879,83.598022,83.086853,82.600090,82.303383,82.190674</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>82.625725,81.819359,81.073982,80.601784,80.218735,79.997437</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:49:03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>89.097694,88.869301,88.831398,88.889610,88.681633,88.673012</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>88.764229,88.337067,88.295113,88.148735,87.762360,87.646194</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>86.598434,85.664627,85.104111,84.656898,84.032173,83.525192</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>87.577927,86.958282,86.517250,86.362801,85.777565,85.473648</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>88.67301177978516</v>
+      </c>
+      <c r="G34" t="n">
+        <v>93.97000122070312</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.296989440917969</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.636894085461559</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.133425813910046</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:42:07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>94.08006286621094</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>89.097694,88.869301,88.831398,88.889610,88.681633,88.673012</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>90.379997,90.260002,91.320000,90.940002,93.570000,93.970001</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1.282303,1.390701,2.488602,2.050392,4.888367,5.296989</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.418791,1.540772,2.725144,2.254665,5.224288,5.636894</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3.133425813910046</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>88.764229,88.337067,88.295113,88.148735,87.762360,87.646194</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>87.577927,86.958282,86.517250,86.362801,85.777565,85.473648</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:42:07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>94.060791,93.868378,93.989769,94.209846,94.068077,94.080063</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>93.776314,92.994095,93.836617,93.287590,93.125145,92.725105</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>90.966278,89.806000,88.998657,88.347481,87.620949,86.765961</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>92.177643,91.574432,90.933853,90.913414,90.112289,89.543732</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>94.08006286621094</v>
+      </c>
+      <c r="G35" t="n">
+        <v>96</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.919937133789062</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.999934514363607</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.7671941035222979</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:52:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>96.00263214111328</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>94.060791,93.868378,93.989769,94.209846,94.068077,94.080063</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>94.430000,93.269997,93.070000,94.480003,93.790001,96.000000</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.369209,0.598381,0.919769,0.270157,0.278076,1.919937</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.390987,0.641558,0.988255,0.285941,0.296488,1.999934</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.7671941035222979</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>93.776314,92.994095,93.836617,93.287590,93.125145,92.725105</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>92.177643,91.574432,90.933853,90.913414,90.112289,89.543732</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:52:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>95.717224,95.560242,95.643082,95.898132,95.912415,96.002632</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>95.349770,94.871574,95.479233,95.322281,95.134529,94.975067</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>92.861710,91.934113,91.354240,90.959419,90.641541,89.895363</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>93.906662,93.441437,92.893967,93.069954,92.539207,92.033073</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>96.00263214111328</v>
+      </c>
+      <c r="G36" t="n">
+        <v>94.18000030517578</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.8226318359375</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.935264206871461</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.37743388176646</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:38</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>93.80326080322266</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>95.717224,95.560242,95.643082,95.898132,95.912415,96.002632</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>92.430000,94.599998,95.330002,95.050003,95.400002,94.180000</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3.287224,0.960244,0.313080,0.848129,0.512413,1.822632</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3.556447,1.015057,0.328417,0.892298,0.537121,1.935264</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1.37743388176646</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>95.349770,94.871574,95.479233,95.322281,95.134529,94.975067</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>93.906662,93.441437,92.893967,93.069954,92.539207,92.033073</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:38</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>94.398712,94.307800,94.189613,94.132133,93.891945,93.803261</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>94.141937,93.798637,94.017113,93.806519,93.375481,93.524933</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>92.259743,91.640953,91.017418,90.619400,90.127609,89.555908</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>93.030571,92.723457,92.099792,92.151794,91.634933,91.172989</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>93.80326080322266</v>
+      </c>
+      <c r="G37" t="n">
+        <v>101.4599990844727</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7.65673828125</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.54655859485591</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.854387595457927</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:58</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>99.93582916259766</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>94.398712,94.307800,94.189613,94.132133,93.891945,93.803261</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>94.050003,95.820000,96.430000,96.519997,96.629997,101.459999</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.348709,1.512200,2.240387,2.387864,2.738052,7.656738</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.370770,1.578167,2.323330,2.473957,2.833543,7.546558</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2.854387595457927</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>94.141937,93.798637,94.017113,93.806519,93.375481,93.524933</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>93.030571,92.723457,92.099792,92.151794,91.634933,91.172989</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:58</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>100.698349,99.986588,99.840797,100.069351,99.894333,99.935829</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>100.295860,99.799934,99.399948,99.502281,99.199516,99.235062</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>97.291916,95.699951,95.017090,94.802208,94.449883,94.205391</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>98.376945,97.136467,96.505943,96.784737,96.336617,95.948715</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>99.93582916259766</v>
+      </c>
+      <c r="G38" t="n">
+        <v>97.04000091552734</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.895828247070312</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.984159336098019</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.86535105922381</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>94.1358642578125</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>100.698349,99.986588,99.840797,100.069351,99.894333,99.935829</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>100.199997,98.589996,98.379997,97.970001,97.300003,97.040001</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.498352,1.396592,1.460800,2.099350,2.594330,2.895828</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.497357,1.416565,1.484854,2.142850,2.666321,2.984159</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1.86535105922381</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>100.295860,99.799934,99.399948,99.502281,99.199516,99.235062</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>98.376945,97.136467,96.505943,96.784737,96.336617,95.948715</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>96.318810,96.100258,95.793480,95.409637,94.790123,94.135864</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>96.048164,95.383820,95.135429,94.389511,93.802757,93.246880</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>94.367783,92.952240,91.327599,89.788017,88.645851,86.908180</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>95.062668,94.243500,93.060623,92.316147,91.038231,89.636551</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>94.1358642578125</v>
+      </c>
+      <c r="G39" t="n">
+        <v>101.0500030517578</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.914138793945312</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6.842294492958986</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.861568112810964</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>101.6999359130859</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>96.318810,96.100258,95.793480,95.409637,94.790123,94.135864</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>96.930000,97.019997,95.940002,96.800003,102.099998,101.050003</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.611190,0.919739,0.146522,1.390366,7.309875,6.914139</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.630548,0.947989,0.152723,1.436329,7.159526,6.842295</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>2.861568112810964</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>96.048164,95.383820,95.135429,94.389511,93.802757,93.246880</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>95.062668,94.243500,93.060623,92.316147,91.038231,89.636551</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>103.924820,103.573318,103.169022,102.799545,102.090363,101.699936</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>103.354736,103.032578,102.146820,101.422897,100.598389,100.022461</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>101.143753,99.229141,97.443207,95.507004,94.185562,92.732422</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>102.006607,100.904526,99.473419,98.645401,97.237411,95.965485</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>101.6999359130859</v>
+      </c>
+      <c r="G40" t="n">
+        <v>106.4800033569336</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.780067443847699</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.489169133310736</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.372283098176175</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:29</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>104.9489288330078</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>103.924820,103.573318,103.169022,102.799545,102.090363,101.699936</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>107.199997,109.440002,109.180000,106.870003,106.360001,106.480003</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.275177,5.866684,6.010978,4.070458,4.269638,4.780067</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3.055202,5.360640,5.505567,3.808794,4.014326,4.489169</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>4.372283098176175</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>103.354736,103.032578,102.146820,101.422897,100.598389,100.022461</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>102.006607,100.904526,99.473419,98.645401,97.237411,95.965485</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:29</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>106.222321,106.153625,105.528320,105.400970,105.030624,104.948929</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>105.973541,105.464737,105.013763,104.444977,104.315231,104.225388</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>103.658173,102.724365,100.958130,100.053375,98.850952,98.574478</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>104.209198,103.732895,102.211472,101.880997,100.885773,100.265594</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>104.9489288330078</v>
+      </c>
+      <c r="G41" t="n">
+        <v>103.5899963378906</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.358932495117173</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.311837574242784</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.511380927972685</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:52:03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>103.1578826904297</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>106.222321,106.153625,105.528320,105.400970,105.030624,104.948929</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>105.290001,103.379997,104.150002,103.870003,103.589996,103.589996</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.932320,2.773628,1.378318,1.530967,1.440628,1.358933</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.885478,2.682944,1.323397,1.473926,1.390702,1.311838</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1.511380927972685</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>105.973541,105.464737,105.013763,104.444977,104.315231,104.225388</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>104.209198,103.732895,102.211472,101.880997,100.885773,100.265594</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:52:03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>103.617241,103.556831,103.255463,103.338242,103.281761,103.157883</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>103.371559,103.660240,103.104614,102.654617,103.246956,103.218468</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>102.329788,101.660217,100.330238,99.795570,99.010971,98.480087</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>102.486504,102.133713,101.103592,101.085075,100.506599,99.765327</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>103.1578826904297</v>
+      </c>
+      <c r="G42" t="n">
+        <v>105.129997253418</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.972114562988267</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.875881874356417</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.538753045873295</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:47</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>105.5951538085938</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>103.617241,103.556831,103.255463,103.338242,103.281761,103.157883</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>103.510002,105.019997,105.370003,105.610001,105.070000,105.129997</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.107239,1.463166,2.114540,2.271759,1.788239,1.972114</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.103602,1.393226,2.006776,2.151083,1.701950,1.875882</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1.538753045873295</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>103.371559,103.660240,103.104614,102.654617,103.246956,103.218468</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>102.486504,102.133713,101.103592,101.085075,100.506599,99.765327</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:47</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>105.240440,105.241890,104.884148,105.260307,105.306244,105.595154</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>105.105370,105.320702,104.918427,105.278755,105.202324,105.733810</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>104.677383,104.243912,102.966492,102.571365,101.970848,101.786682</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>104.805534,104.543831,103.629646,103.890968,103.347076,103.082420</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>105.5951538085938</v>
+      </c>
+      <c r="G43" t="n">
+        <v>101.629997253418</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.965156555175838</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.901561214538441</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.099963018937646</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:19</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>101.5955657958984</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>105.240440,105.241890,104.884148,105.260307,105.306244,105.595154</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>105.120003,106.269997,105.820000,101.760002,101.949997,101.629997</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.120437,1.028107,0.935852,3.500305,3.356247,3.965157</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.114571,0.967448,0.884381,3.439765,3.292052,3.901561</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>2.099963018937646</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>105.105370,105.320702,104.918427,105.278755,105.202324,105.733810</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>104.805534,104.543831,103.629646,103.890968,103.347076,103.082420</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:19</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>101.565826,101.768188,101.589523,101.769203,101.612541,101.595566</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>101.029373,101.649483,101.386131,101.573151,101.632446,101.805504</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>100.224472,100.076424,99.026733,98.903496,98.118309,97.757919</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>100.545029,100.644554,99.886322,100.015053,99.340080,99.063301</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>101.5955657958984</v>
+      </c>
+      <c r="G44" t="n">
+        <v>103.7600021362305</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.164436340332074</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.086002598082354</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.675283457024403</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:49:07</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>104.3905944824219</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>101.565826,101.768188,101.589523,101.769203,101.612541,101.595566</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>103.379997,102.870003,103.620003,103.050003,103.620003,103.760002</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.814171,1.101815,2.030480,1.280800,2.007462,2.164436</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.754857,1.071075,1.959544,1.242892,1.937330,2.086002</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.675283457024403</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>101.029373,101.649483,101.386131,101.573151,101.632446,101.805504</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>100.545029,100.644554,99.886322,100.015053,99.340080,99.063301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:49:07</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>103.734268,103.830086,103.623116,104.056580,104.165138,104.390594</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>103.506294,103.700653,103.428452,103.569099,104.126678,104.790924</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>102.371651,102.116493,101.311699,101.618187,100.980507,101.076508</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>102.615334,102.721931,102.085388,102.411583,102.127266,102.094467</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>104.3905944824219</v>
+      </c>
+      <c r="G45" t="n">
+        <v>99.83999633789062</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.550598144531278</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.557890936945342</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.271580048407368</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>99.18158721923828</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>103.734268,103.830086,103.623116,104.056580,104.165138,104.390594</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>102.260002,102.000000,100.029999,99.730003,100.250000,99.839996</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1.474266,1.830086,3.593117,4.326577,3.915138,4.550598</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1.441684,1.794202,3.592040,4.338290,3.905375,4.557890</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>3.271580048407368</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>103.506294,103.700653,103.428452,103.569099,104.126678,104.790924</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>102.615334,102.721931,102.085388,102.411583,102.127266,102.094467</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>99.611588,99.525536,99.538467,99.407204,99.419708,99.181587</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>99.481865,99.480324,99.397346,99.199837,99.338249,99.559654</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>98.146362,97.730492,97.091827,96.862869,96.436646,95.986603</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>98.774536,98.420792,97.987297,97.875023,97.527298,97.188667</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>99.18158721923828</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100.5800018310547</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.398414611816406</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.390350553150057</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9072376916815481</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:13</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="n">
+        <v>100.1951293945312</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>99.611588,99.525536,99.538467,99.407204,99.419708,99.181587</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>98.070000,99.250000,99.379997,100.400002,100.480003,100.580002</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.541588,0.275536,0.158470,0.992798,1.060295,1.398415</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1.571926,0.277618,0.159458,0.988842,1.055230,1.390351</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9072376916815481</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>99.481865,99.480324,99.397346,99.199837,99.338249,99.559654</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>98.774536,98.420792,97.987297,97.875023,97.527298,97.188667</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:13</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>100.193115,100.297623,100.461250,100.269730,100.227974,100.195129</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>100.121994,100.062561,100.450172,99.920876,100.213470,100.182457</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>98.262154,98.065681,97.684639,97.420113,97.069984,96.719917</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>98.998589,98.929504,98.717102,98.510239,98.148521,98.142845</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>100.1951293945312</v>
+      </c>
+      <c r="G47" t="n">
+        <v>103.629997253418</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.434867858886776</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.314549792457401</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.329284427054901</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:54</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>103.7555084228516</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>100.193115,100.297623,100.461250,100.269730,100.227974,100.195129</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>100.760002,105.160004,105.290001,103.940002,103.709999,103.629997</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.566887,4.862381,4.828751,3.670272,3.482025,3.434868</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.562611,4.623793,4.586144,3.531145,3.357463,3.314550</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>3.329284427054901</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>100.121994,100.062561,100.450172,99.920876,100.213470,100.182457</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>98.998589,98.929504,98.717102,98.510239,98.148521,98.142845</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:54</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>103.420105,103.332382,103.466637,103.426552,103.651352,103.755508</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>103.033173,103.068222,103.525597,103.332794,103.498314,103.794861</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>101.573906,101.291878,100.997307,100.922318,100.709297,100.531898</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>102.224342,102.067619,101.906815,101.840782,101.729347,101.863022</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>103.7555084228516</v>
+      </c>
+      <c r="G48" t="n">
+        <v>101.8399963378906</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.91551208496098</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.880903528909784</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.547409417924261</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>101.7575149536133</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>103.420105,103.332382,103.466637,103.426552,103.651352,103.755508</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>104.080002,101.449997,101.709999,101.940002,101.889999,101.839996</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.659897,1.882385,1.756638,1.486550,1.761353,1.915512</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.634028,1.855481,1.727104,1.458259,1.728681,1.880903</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.547409417924261</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>103.033173,103.068222,103.525597,103.332794,103.498314,103.794861</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>102.224342,102.067619,101.906815,101.840782,101.729347,101.863022</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>101.854622,101.800095,101.845116,101.874908,101.839806,101.757515</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>101.872597,101.567612,101.853752,101.841759,101.593025,101.775780</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>100.219948,99.865074,99.489449,99.354027,98.982849,98.629051</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>100.959923,100.728981,100.375633,100.358086,100.067604,100.017624</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>101.7575149536133</v>
+      </c>
+      <c r="G49" t="n">
+        <v>106.0400009155273</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.282485961914048</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.038557077461292</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.066845476431682</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:41</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>105.368293762207</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>101.854622,101.800095,101.845116,101.874908,101.839806,101.757515</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>102.339996,102.959999,103.419998,103.260002,105.970001,106.040001</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.485374,1.159904,1.574882,1.385094,4.130195,4.282486</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.474276,1.126558,1.522802,1.341366,3.897514,4.038557</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2.066845476431682</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>101.872597,101.567612,101.853752,101.841759,101.593025,101.775780</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>100.959923,100.728981,100.375633,100.358086,100.067604,100.017624</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:41</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>105.655968,105.536957,105.537415,105.492134,105.501488,105.368294</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>105.484039,105.389893,105.609291,105.492821,105.545532,105.489342</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>103.430069,103.036018,102.573097,102.501785,102.175133,101.955070</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>104.219376,103.958046,103.680832,103.601768,103.402657,103.215546</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>105.368293762207</v>
+      </c>
+      <c r="G50" t="n">
+        <v>105.0800018310547</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.2882919311523153</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2743547070124958</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4656949677923083</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:58</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>104.6838989257812</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>105.655968,105.536957,105.537415,105.492134,105.501488,105.368294</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>106.459999,105.739998,105.489998,106.559998,104.949997,105.080002</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.804031,0.203041,0.047417,1.067864,0.551491,0.288292</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.755242,0.192019,0.044949,1.002124,0.525480,0.274355</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4656949677923083</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>105.484039,105.389893,105.609291,105.492821,105.545532,105.489342</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>104.219376,103.958046,103.680832,103.601768,103.402657,103.215546</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:58</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>105.112503,105.104668,105.035202,104.921051,104.902237,104.683899</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>104.882591,105.010231,105.037849,104.802956,104.985031,104.497505</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>103.340164,103.022659,102.713997,102.601501,102.153168,101.927719</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>104.020897,103.855965,103.544121,103.479652,103.237442,102.955688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>104.6838989257812</v>
+      </c>
+      <c r="G51" t="n">
+        <v>103.1699981689453</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.513900756835881</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.467384689061255</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.120899807647276</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:45</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>102.6860427856445</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>105.112503,105.104668,105.035202,104.921051,104.902237,104.683899</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>104.919998,103.220001,104.370003,103.790001,103.330002,103.169998</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.192505,1.884667,0.665199,1.131050,1.572235,1.513901</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.183478,1.825874,0.637347,1.089749,1.521567,1.467385</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1.120899807647276</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>104.882591,105.010231,105.037849,104.802956,104.985031,104.497505</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>104.020897,103.855965,103.544121,103.479652,103.237442,102.955688</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:45</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>103.187019,103.355057,102.966187,102.849327,102.772728,102.686043</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>103.143845,103.416176,103.106850,102.558304,102.758492,102.175133</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>101.414734,101.311661,100.700081,100.559433,100.128220,100.133781</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>102.014786,102.017815,101.501823,101.392273,101.128242,100.935616</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>102.6860427856445</v>
+      </c>
+      <c r="G52" t="n">
+        <v>103.7900009155273</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.103958129882841</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.063645939054698</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.5945637756990284</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>103.5477752685547</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>103.187019,103.355057,102.966187,102.849327,102.772728,102.686043</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>102.839996,104.279999,103.230003,103.370003,103.309998,103.790001</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.347023,0.924942,0.263816,0.520676,0.537270,1.103958</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.337439,0.886979,0.255562,0.503701,0.520056,1.063646</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.5945637756990284</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>103.143845,103.416176,103.106850,102.558304,102.758492,102.175133</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>102.014786,102.017815,101.501823,101.392273,101.128242,100.935616</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>103.603447,103.734886,103.671295,103.425926,103.527809,103.547775</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>103.622742,103.805489,103.600441,102.848930,103.439011,103.008698</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>101.774330,101.462898,101.092064,100.890266,100.672218,100.919449</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>102.265808,102.214386,102.057274,101.825844,101.870506,101.751427</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>103.5477752685547</v>
+      </c>
+      <c r="G53" t="n">
+        <v>102.0500030517578</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.497772216796889</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.467684636949249</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.241449617205863</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="n">
+        <v>101.7576293945312</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>103.603447,103.734886,103.671295,103.425926,103.527809,103.547775</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>104.220001,103.050003,102.300003,101.699997,101.809998,102.050003</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.616554,0.684883,1.371292,1.725929,1.717811,1.497772</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.591589,0.664612,1.340461,1.697079,1.687272,1.467684</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1.241449617205863</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>103.622742,103.805489,103.600441,102.848930,103.439011,103.008698</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>102.265808,102.214386,102.057274,101.825844,101.870506,101.751427</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>101.830894,101.852211,101.809090,101.818260,101.781067,101.757629</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>101.994591,102.203209,101.775627,101.822586,102.131050,101.499390</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>100.421364,100.243927,99.885345,99.770508,99.463081,99.507973</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>100.853828,100.734299,100.496094,100.501656,100.284378,100.218750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>101.7576293945312</v>
+      </c>
+      <c r="G54" t="n">
+        <v>99.43000030517578</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.327629089355412</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.34097262618056</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.217028323729554</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:56</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>99.15017700195312</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>101.830894,101.852211,101.809090,101.818260,101.781067,101.757629</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>100.980003,99.699997,99.629997,98.610001,99.279999,99.430000</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0.850891,2.152214,2.179093,3.208259,2.501068,2.327629</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.842633,2.158690,2.187185,3.253483,2.519207,2.340972</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>2.217028323729554</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>101.994591,102.203209,101.775627,101.822586,102.131050,101.499390</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>100.853828,100.734299,100.496094,100.501656,100.284378,100.218750</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:56</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>99.313225,99.252174,99.330406,99.257187,99.247398,99.150177</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>99.363144,99.368073,99.070587,99.491364,99.443665,99.113029</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>97.827042,97.355476,97.093155,96.882568,96.526840,96.285385</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>98.230995,97.962387,97.840141,97.587143,97.413055,97.269707</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>99.15017700195312</v>
+      </c>
+      <c r="G55" t="n">
+        <v>101.6100006103516</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.459823608398438</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.420847941760412</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.156427798420722</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:09</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="n">
+        <v>101.0630035400391</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>99.313225,99.252174,99.330406,99.257187,99.247398,99.150177</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>99.470001,101.580002,102.000000,102.449997,101.620003,101.610001</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.156776,2.327828,2.669594,3.192810,2.372605,2.459824</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.157612,2.291620,2.617249,3.116457,2.334781,2.420848</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.156427798420722</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>99.363144,99.368073,99.070587,99.491364,99.443665,99.113029</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>98.230995,97.962387,97.840141,97.587143,97.413055,97.269707</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:09</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>101.577873,101.550461,101.640404,100.865425,101.606316,101.063004</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>101.164444,101.631264,100.902206,100.432457,101.710945,100.275215</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>99.675003,98.754501,98.802681,97.710297,97.995316,97.269630</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>100.163795,99.712120,99.949821,98.769012,99.633232,98.592705</t>
         </is>
       </c>
     </row>
